--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frank\OneDrive\Documents\UiPath\UiPath_RPA_Adriana_Carrillo\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E739714-C405-40DC-86A1-F5883DC9D265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D519D4A-36B3-4B1C-BB25-5585DA912FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1817" yWindow="1817" windowWidth="16457" windowHeight="8966" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
   <si>
     <t>Name</t>
   </si>
@@ -173,6 +173,15 @@
   </si>
   <si>
     <t>Output\ContactosReporte.xlsx</t>
+  </si>
+  <si>
+    <t>varApellido</t>
+  </si>
+  <si>
+    <t>varProvincia</t>
+  </si>
+  <si>
+    <t>varCorreo</t>
   </si>
 </sst>
 </file>
@@ -664,10 +673,29 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A9" s="4"/>
+      <c r="A9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
@@ -1713,7 +1741,7 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>23</v>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frank\OneDrive\Documents\UiPath\UiPath_RPA_Adriana_Carrillo\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D519D4A-36B3-4B1C-BB25-5585DA912FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBCAF15-402E-4941-BEB3-B985444CE941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1817" yWindow="1817" windowWidth="16457" windowHeight="8966" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
   <si>
     <t>Name</t>
   </si>
@@ -172,16 +172,7 @@
     <t>MaxPages</t>
   </si>
   <si>
-    <t>Output\ContactosReporte.xlsx</t>
-  </si>
-  <si>
-    <t>varApellido</t>
-  </si>
-  <si>
-    <t>varProvincia</t>
-  </si>
-  <si>
-    <t>varCorreo</t>
+    <t>C:\Users\Frank\OneDrive\Documents\UiPath\UiPath_RPA_Adriana_Carrillo\Data\Output\ContactosReporte.xlsx</t>
   </si>
 </sst>
 </file>
@@ -570,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z995"/>
+  <dimension ref="A1:Z992"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.4609375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.53515625" customWidth="1"/>
@@ -669,33 +660,12 @@
         <v>48</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
@@ -1677,9 +1647,6 @@
     <row r="990" ht="14.25" customHeight="1"/>
     <row r="991" ht="14.25" customHeight="1"/>
     <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <hyperlinks>
